--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41007-2026 artfynd.xlsx
+++ b/artfynd/A 41007-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007664</v>
       </c>
       <c r="B2" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007665</v>
       </c>
       <c r="B3" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
